--- a/Chapter05_Campylobacter_plasmids/Appendix/Appendix07_metadata_plasmids_Nanopore.xlsx
+++ b/Chapter05_Campylobacter_plasmids/Appendix/Appendix07_metadata_plasmids_Nanopore.xlsx
@@ -1,26 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://masseyuni.sharepoint.com/teams/Students-AlineParolin/Shared Documents/Aline Parolin Calarga PhD Project/Thesis/Chapter 05 Campy plasmids/Writing_Chapter05/Appendix/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="164" documentId="8_{7DD50868-0E31-4750-8C1D-5ED6A936E02D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{226292D9-579E-48F3-B2FF-03B3714E537C}"/>
+  <xr:revisionPtr revIDLastSave="168" documentId="8_{7DD50868-0E31-4750-8C1D-5ED6A936E02D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5832B3F-D6BC-444B-839E-2F67B6A2A2EC}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{DA16D0B6-C423-44EC-8F1C-1B110CEF8D52}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DA16D0B6-C423-44EC-8F1C-1B110CEF8D52}"/>
   </bookViews>
   <sheets>
     <sheet name="Plasmids" sheetId="1" r:id="rId1"/>
-    <sheet name="M4R59S3V1" sheetId="3" r:id="rId2"/>
-    <sheet name="Isolates_without_plasmid" sheetId="2" r:id="rId3"/>
+    <sheet name="Isolates_without_plasmid" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plasmids!$A$1:$L$81</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="195">
   <si>
     <t>ID</t>
   </si>
@@ -52,21 +51,27 @@
     <t>ST</t>
   </si>
   <si>
+    <t>WG_GC_content</t>
+  </si>
+  <si>
+    <t>Assembly method</t>
+  </si>
+  <si>
+    <t>Dendrogram_plasmid_ID</t>
+  </si>
+  <si>
+    <t>RFPlasmid votes plasmid</t>
+  </si>
+  <si>
+    <t>Plasmid_markers</t>
+  </si>
+  <si>
     <t>contig_length</t>
   </si>
   <si>
-    <t>WG_GC_content</t>
-  </si>
-  <si>
     <t>GC_content_plasmid</t>
   </si>
   <si>
-    <t>Assembly method</t>
-  </si>
-  <si>
-    <t>Plasmid_markers</t>
-  </si>
-  <si>
     <t>Bandage_circular</t>
   </si>
   <si>
@@ -79,18 +84,21 @@
     <t>jejuni</t>
   </si>
   <si>
+    <t>Unicycler</t>
+  </si>
+  <si>
     <t>SC0014_ST520_p1</t>
   </si>
   <si>
-    <t>Unicycler</t>
-  </si>
-  <si>
     <t>R10</t>
   </si>
   <si>
     <t>no</t>
   </si>
   <si>
+    <t>non-mobilisable</t>
+  </si>
+  <si>
     <t>SC0014_ST520_p3</t>
   </si>
   <si>
@@ -100,6 +108,9 @@
     <t>circular</t>
   </si>
   <si>
+    <t>conjugative</t>
+  </si>
+  <si>
     <t>SC0014_ST520_p2</t>
   </si>
   <si>
@@ -154,12 +165,12 @@
     <t>SC0134</t>
   </si>
   <si>
+    <t>Flye</t>
+  </si>
+  <si>
     <t>SC0134_ST535</t>
   </si>
   <si>
-    <t>Flye</t>
-  </si>
-  <si>
     <t>R59</t>
   </si>
   <si>
@@ -172,9 +183,6 @@
     <t>SC0158_ST42_p1</t>
   </si>
   <si>
-    <t>conjugative</t>
-  </si>
-  <si>
     <t>SC0158_ST42_p2</t>
   </si>
   <si>
@@ -541,12 +549,6 @@
     <t>SC1718_ST3230_p1</t>
   </si>
   <si>
-    <t>RFPlasmid votes plasmid</t>
-  </si>
-  <si>
-    <t>Dendrogram_plasmid_ID</t>
-  </si>
-  <si>
     <t>Plasmid type</t>
   </si>
   <si>
@@ -559,18 +561,30 @@
     <t xml:space="preserve">Evidence of mobility </t>
   </si>
   <si>
+    <t>CC</t>
+  </si>
+  <si>
+    <t>Host</t>
+  </si>
+  <si>
     <t>SC0001</t>
   </si>
   <si>
+    <t>No plasmids detected</t>
+  </si>
+  <si>
     <t>NA</t>
   </si>
   <si>
-    <t>No plasmids detected</t>
+    <t>Ovine</t>
   </si>
   <si>
     <t>SC0017</t>
   </si>
   <si>
+    <t>Human</t>
+  </si>
+  <si>
     <t>SC0028</t>
   </si>
   <si>
@@ -583,9 +597,15 @@
     <t>SC0109</t>
   </si>
   <si>
+    <t>Poultry</t>
+  </si>
+  <si>
     <t>SC0119</t>
   </si>
   <si>
+    <t>Bovine</t>
+  </si>
+  <si>
     <t>SC0154</t>
   </si>
   <si>
@@ -605,36 +625,6 @@
   </si>
   <si>
     <t>SC1449</t>
-  </si>
-  <si>
-    <t>CC</t>
-  </si>
-  <si>
-    <t>Host</t>
-  </si>
-  <si>
-    <t>Ovine</t>
-  </si>
-  <si>
-    <t>Human</t>
-  </si>
-  <si>
-    <t>Poultry</t>
-  </si>
-  <si>
-    <t>Bovine</t>
-  </si>
-  <si>
-    <t>tetO in the chromosome?</t>
-  </si>
-  <si>
-    <t>plasmid</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>non-mobilisable</t>
   </si>
 </sst>
 </file>
@@ -1059,39 +1049,39 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>166</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>520</v>
@@ -1100,16 +1090,16 @@
         <v>30.34</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2">
         <v>0.95079999999999998</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I2" s="1">
         <v>18794</v>
@@ -1118,18 +1108,18 @@
         <v>23.86</v>
       </c>
       <c r="K2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L2" t="s">
-        <v>197</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>520</v>
@@ -1138,16 +1128,16 @@
         <v>30.34</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G3">
         <v>0.99239999999999995</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I3" s="1">
         <v>39597</v>
@@ -1156,18 +1146,18 @@
         <v>27.28</v>
       </c>
       <c r="K3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L3" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4">
         <v>520</v>
@@ -1176,16 +1166,16 @@
         <v>30.34</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G4">
         <v>0.99139999999999995</v>
       </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I4" s="1">
         <v>36323</v>
@@ -1194,18 +1184,18 @@
         <v>26.07</v>
       </c>
       <c r="K4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L4" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>677</v>
@@ -1214,16 +1204,16 @@
         <v>30.37</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G5">
         <v>0.93820000000000003</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I5" s="1">
         <v>40676</v>
@@ -1232,18 +1222,18 @@
         <v>26.01</v>
       </c>
       <c r="K5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L5" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6">
         <v>48</v>
@@ -1252,16 +1242,16 @@
         <v>30.45</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G6">
         <v>0.98839999999999995</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I6" s="1">
         <v>43663</v>
@@ -1270,18 +1260,18 @@
         <v>27.42</v>
       </c>
       <c r="K6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L6" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7">
         <v>704</v>
@@ -1290,16 +1280,16 @@
         <v>29.76</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G7">
         <v>0.84260000000000002</v>
       </c>
       <c r="H7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I7" s="1">
         <v>4468</v>
@@ -1308,18 +1298,18 @@
         <v>29.63</v>
       </c>
       <c r="K7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" t="s">
         <v>18</v>
-      </c>
-      <c r="L7" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8">
         <v>1030</v>
@@ -1328,16 +1318,16 @@
         <v>30.17</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G8">
         <v>0.96660000000000001</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I8" s="1">
         <v>38820</v>
@@ -1346,18 +1336,18 @@
         <v>27.36</v>
       </c>
       <c r="K8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L8" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C9">
         <v>61</v>
@@ -1366,16 +1356,16 @@
         <v>30.44</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G9">
         <v>0.9728</v>
       </c>
       <c r="H9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I9" s="1">
         <v>29822</v>
@@ -1384,18 +1374,18 @@
         <v>28.34</v>
       </c>
       <c r="K9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L9" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C10">
         <v>137</v>
@@ -1404,16 +1394,16 @@
         <v>30.3</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G10">
         <v>0.79679999999999995</v>
       </c>
       <c r="H10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I10" s="1">
         <v>50038</v>
@@ -1422,18 +1412,18 @@
         <v>22.79</v>
       </c>
       <c r="K10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L10" t="s">
-        <v>197</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>535</v>
@@ -1442,16 +1432,16 @@
         <v>30.62</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G11">
         <v>0.90159999999999996</v>
       </c>
       <c r="H11" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I11" s="1">
         <v>124814</v>
@@ -1460,18 +1450,18 @@
         <v>26.76</v>
       </c>
       <c r="K11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C12">
         <v>42</v>
@@ -1480,13 +1470,13 @@
         <v>30.48</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F12" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H12" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I12" s="1">
         <v>43614</v>
@@ -1495,18 +1485,18 @@
         <v>27.4</v>
       </c>
       <c r="K12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L12" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C13">
         <v>42</v>
@@ -1515,13 +1505,13 @@
         <v>30.48</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I13" s="1">
         <v>30067</v>
@@ -1530,18 +1520,18 @@
         <v>30.06</v>
       </c>
       <c r="K13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L13" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C14">
         <v>2026</v>
@@ -1550,16 +1540,16 @@
         <v>30.29</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G14">
         <v>0.93340000000000001</v>
       </c>
       <c r="H14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I14" s="1">
         <v>25981</v>
@@ -1568,18 +1558,18 @@
         <v>25.93</v>
       </c>
       <c r="K14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L14" t="s">
-        <v>197</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C15">
         <v>3610</v>
@@ -1588,16 +1578,16 @@
         <v>30.27</v>
       </c>
       <c r="E15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G15">
         <v>0.98040000000000005</v>
       </c>
       <c r="H15" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I15" s="1">
         <v>28043</v>
@@ -1606,18 +1596,18 @@
         <v>28.08</v>
       </c>
       <c r="K15" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L15" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C16">
         <v>3610</v>
@@ -1626,16 +1616,16 @@
         <v>30.27</v>
       </c>
       <c r="E16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F16" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G16">
         <v>0.99380000000000002</v>
       </c>
       <c r="H16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I16" s="1">
         <v>42058</v>
@@ -1644,18 +1634,18 @@
         <v>27.08</v>
       </c>
       <c r="K16" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L16" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C17">
         <v>520</v>
@@ -1664,16 +1654,16 @@
         <v>30.46</v>
       </c>
       <c r="E17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F17" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G17">
         <v>0.97760000000000002</v>
       </c>
       <c r="H17" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I17" s="1">
         <v>30064</v>
@@ -1682,18 +1672,18 @@
         <v>28.26</v>
       </c>
       <c r="K17" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L17" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C18">
         <v>520</v>
@@ -1702,16 +1692,16 @@
         <v>30.46</v>
       </c>
       <c r="E18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G18">
         <v>0.99380000000000002</v>
       </c>
       <c r="H18" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I18" s="1">
         <v>42062</v>
@@ -1720,18 +1710,18 @@
         <v>27.08</v>
       </c>
       <c r="K18" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L18" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B19" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C19">
         <v>3222</v>
@@ -1740,16 +1730,16 @@
         <v>31.38</v>
       </c>
       <c r="E19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G19">
         <v>0.81640000000000001</v>
       </c>
       <c r="H19" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I19" s="1">
         <v>4060</v>
@@ -1758,18 +1748,18 @@
         <v>29.95</v>
       </c>
       <c r="K19" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L19" t="s">
-        <v>197</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C20">
         <v>22</v>
@@ -1778,16 +1768,16 @@
         <v>30.43</v>
       </c>
       <c r="E20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F20" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G20">
         <v>0.98660000000000003</v>
       </c>
       <c r="H20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I20" s="1">
         <v>39851</v>
@@ -1796,18 +1786,18 @@
         <v>27.34</v>
       </c>
       <c r="K20" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L20" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C21">
         <v>1115</v>
@@ -1816,16 +1806,16 @@
         <v>31.24</v>
       </c>
       <c r="E21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F21" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G21">
         <v>0.96499999999999997</v>
       </c>
       <c r="H21" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I21" s="1">
         <v>27538</v>
@@ -1834,18 +1824,18 @@
         <v>28.99</v>
       </c>
       <c r="K21" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L21" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C22">
         <v>4009</v>
@@ -1854,16 +1844,16 @@
         <v>31.35</v>
       </c>
       <c r="E22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F22" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G22">
         <v>0.94079999999999997</v>
       </c>
       <c r="H22" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I22" s="1">
         <v>36479</v>
@@ -1872,18 +1862,18 @@
         <v>28.16</v>
       </c>
       <c r="K22" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L22" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C23">
         <v>48</v>
@@ -1892,16 +1882,16 @@
         <v>30.45</v>
       </c>
       <c r="E23" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F23" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G23">
         <v>0.98819999999999997</v>
       </c>
       <c r="H23" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I23" s="1">
         <v>43665</v>
@@ -1910,18 +1900,18 @@
         <v>27.4</v>
       </c>
       <c r="K23" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L23" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C24">
         <v>42</v>
@@ -1930,16 +1920,16 @@
         <v>30.57</v>
       </c>
       <c r="E24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G24">
         <v>0.96879999999999999</v>
       </c>
       <c r="H24" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I24" s="1">
         <v>26570</v>
@@ -1948,18 +1938,18 @@
         <v>29.18</v>
       </c>
       <c r="K24" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L24" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C25">
         <v>48</v>
@@ -1968,16 +1958,16 @@
         <v>30.47</v>
       </c>
       <c r="E25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G25">
         <v>0.98880000000000001</v>
       </c>
       <c r="H25" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I25" s="1">
         <v>43678</v>
@@ -1986,18 +1976,18 @@
         <v>27.42</v>
       </c>
       <c r="K25" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L25" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C26">
         <v>61</v>
@@ -2006,16 +1996,16 @@
         <v>30.4</v>
       </c>
       <c r="E26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F26" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G26">
         <v>0.99219999999999997</v>
       </c>
       <c r="H26" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I26" s="1">
         <v>36559</v>
@@ -2024,18 +2014,18 @@
         <v>26.05</v>
       </c>
       <c r="K26" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L26" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C27">
         <v>422</v>
@@ -2044,16 +2034,16 @@
         <v>30.36</v>
       </c>
       <c r="E27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F27" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G27">
         <v>0.99299999999999999</v>
       </c>
       <c r="H27" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I27" s="1">
         <v>36268</v>
@@ -2062,18 +2052,18 @@
         <v>26.04</v>
       </c>
       <c r="K27" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L27" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C28">
         <v>12762</v>
@@ -2082,16 +2072,16 @@
         <v>30.37</v>
       </c>
       <c r="E28" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F28" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G28">
         <v>0.99260000000000004</v>
       </c>
       <c r="H28" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I28" s="1">
         <v>39586</v>
@@ -2100,18 +2090,18 @@
         <v>27.28</v>
       </c>
       <c r="K28" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L28" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C29">
         <v>12762</v>
@@ -2120,16 +2110,16 @@
         <v>30.37</v>
       </c>
       <c r="E29" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F29" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G29">
         <v>0.98040000000000005</v>
       </c>
       <c r="H29" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I29" s="1">
         <v>27689</v>
@@ -2138,18 +2128,18 @@
         <v>28.12</v>
       </c>
       <c r="K29" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L29" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C30">
         <v>422</v>
@@ -2158,16 +2148,16 @@
         <v>30.32</v>
       </c>
       <c r="E30" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F30" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G30">
         <v>0.9728</v>
       </c>
       <c r="H30" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I30" s="1">
         <v>29581</v>
@@ -2176,18 +2166,18 @@
         <v>28.2</v>
       </c>
       <c r="K30" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L30" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C31">
         <v>422</v>
@@ -2196,16 +2186,16 @@
         <v>30.32</v>
       </c>
       <c r="E31" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F31" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G31">
         <v>0.99519999999999997</v>
       </c>
       <c r="H31" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I31" s="1">
         <v>40695</v>
@@ -2214,18 +2204,18 @@
         <v>27.4</v>
       </c>
       <c r="K31" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L31" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B32" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C32">
         <v>6964</v>
@@ -2234,16 +2224,16 @@
         <v>30.47</v>
       </c>
       <c r="E32" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F32" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G32">
         <v>0.99299999999999999</v>
       </c>
       <c r="H32" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I32" s="1">
         <v>45668</v>
@@ -2252,18 +2242,18 @@
         <v>27.3</v>
       </c>
       <c r="K32" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L32" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B33" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C33">
         <v>830</v>
@@ -2272,16 +2262,16 @@
         <v>30.94</v>
       </c>
       <c r="E33" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G33">
         <v>0.93820000000000003</v>
       </c>
       <c r="H33" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I33" s="1">
         <v>16202</v>
@@ -2290,18 +2280,18 @@
         <v>26</v>
       </c>
       <c r="K33" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L33" t="s">
-        <v>197</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B34" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C34">
         <v>830</v>
@@ -2310,16 +2300,16 @@
         <v>30.94</v>
       </c>
       <c r="E34" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F34" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G34">
         <v>0.95760000000000001</v>
       </c>
       <c r="H34" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I34" s="1">
         <v>181199</v>
@@ -2328,18 +2318,18 @@
         <v>26.45</v>
       </c>
       <c r="K34" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L34" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C35">
         <v>42</v>
@@ -2348,16 +2338,16 @@
         <v>30.5</v>
       </c>
       <c r="E35" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F35" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G35">
         <v>0.96199999999999997</v>
       </c>
       <c r="H35" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I35" s="1">
         <v>26177</v>
@@ -2366,18 +2356,18 @@
         <v>29.16</v>
       </c>
       <c r="K35" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L35" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C36">
         <v>42</v>
@@ -2386,16 +2376,16 @@
         <v>30.5</v>
       </c>
       <c r="E36" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F36" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G36">
         <v>0.99219999999999997</v>
       </c>
       <c r="H36" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I36" s="1">
         <v>36555</v>
@@ -2404,18 +2394,18 @@
         <v>26.05</v>
       </c>
       <c r="K36" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L36" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C37">
         <v>42</v>
@@ -2424,16 +2414,16 @@
         <v>30.47</v>
       </c>
       <c r="E37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F37" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G37">
         <v>0.97740000000000005</v>
       </c>
       <c r="H37" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I37" s="1">
         <v>30064</v>
@@ -2442,18 +2432,18 @@
         <v>28.25</v>
       </c>
       <c r="K37" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L37" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C38">
         <v>3232</v>
@@ -2462,16 +2452,16 @@
         <v>31.33</v>
       </c>
       <c r="E38" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F38" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G38">
         <v>0.99280000000000002</v>
       </c>
       <c r="H38" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I38" s="1">
         <v>36918</v>
@@ -2480,18 +2470,18 @@
         <v>25.99</v>
       </c>
       <c r="K38" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L38" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B39" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C39">
         <v>14595</v>
@@ -2500,16 +2490,16 @@
         <v>31.39</v>
       </c>
       <c r="E39" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F39" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G39">
         <v>0.98819999999999997</v>
       </c>
       <c r="H39" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I39" s="1">
         <v>43676</v>
@@ -2518,18 +2508,18 @@
         <v>27.42</v>
       </c>
       <c r="K39" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L39" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B40" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C40">
         <v>900</v>
@@ -2538,16 +2528,16 @@
         <v>30.89</v>
       </c>
       <c r="E40" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F40" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G40">
         <v>0.83940000000000003</v>
       </c>
       <c r="H40" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I40" s="1">
         <v>2415</v>
@@ -2556,18 +2546,18 @@
         <v>26.13</v>
       </c>
       <c r="K40" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L40" t="s">
-        <v>197</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B41" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C41">
         <v>900</v>
@@ -2576,16 +2566,16 @@
         <v>30.89</v>
       </c>
       <c r="E41" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F41" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G41">
         <v>0.78339999999999999</v>
       </c>
       <c r="H41" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I41" s="1">
         <v>4860</v>
@@ -2594,18 +2584,18 @@
         <v>31.48</v>
       </c>
       <c r="K41" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L41" t="s">
-        <v>197</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B42" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C42">
         <v>900</v>
@@ -2614,16 +2604,16 @@
         <v>30.89</v>
       </c>
       <c r="E42" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F42" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G42">
         <v>0.83919999999999995</v>
       </c>
       <c r="H42" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I42" s="1">
         <v>2418</v>
@@ -2632,18 +2622,18 @@
         <v>26.3</v>
       </c>
       <c r="K42" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L42" t="s">
-        <v>197</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B43" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C43">
         <v>900</v>
@@ -2652,16 +2642,16 @@
         <v>30.89</v>
       </c>
       <c r="E43" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F43" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G43">
         <v>0.70520000000000005</v>
       </c>
       <c r="H43" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="I43" s="1">
         <v>2099</v>
@@ -2670,18 +2660,18 @@
         <v>31.35</v>
       </c>
       <c r="K43" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L43" t="s">
-        <v>197</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B44" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C44">
         <v>900</v>
@@ -2690,16 +2680,16 @@
         <v>30.89</v>
       </c>
       <c r="E44" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F44" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G44">
         <v>0.95779999999999998</v>
       </c>
       <c r="H44" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I44" s="1">
         <v>35851</v>
@@ -2708,18 +2698,18 @@
         <v>28.62</v>
       </c>
       <c r="K44" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L44" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C45">
         <v>900</v>
@@ -2728,16 +2718,16 @@
         <v>30.89</v>
       </c>
       <c r="E45" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F45" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G45">
         <v>0.94979999999999998</v>
       </c>
       <c r="H45" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I45" s="1">
         <v>28368</v>
@@ -2746,18 +2736,18 @@
         <v>29.17</v>
       </c>
       <c r="K45" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L45" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B46" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C46">
         <v>900</v>
@@ -2766,16 +2756,16 @@
         <v>30.89</v>
       </c>
       <c r="E46" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F46" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G46">
         <v>0.96760000000000002</v>
       </c>
       <c r="H46" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I46" s="1">
         <v>35395</v>
@@ -2784,18 +2774,18 @@
         <v>26.02</v>
       </c>
       <c r="K46" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L46" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B47" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C47">
         <v>5734</v>
@@ -2804,16 +2794,16 @@
         <v>31.36</v>
       </c>
       <c r="E47" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F47" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G47">
         <v>0.9748</v>
       </c>
       <c r="H47" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I47" s="1">
         <v>46278</v>
@@ -2822,18 +2812,18 @@
         <v>28.3</v>
       </c>
       <c r="K47" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L47" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B48" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C48">
         <v>14186</v>
@@ -2842,16 +2832,16 @@
         <v>30.28</v>
       </c>
       <c r="E48" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F48" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G48">
         <v>0.99099999999999999</v>
       </c>
       <c r="H48" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I48" s="1">
         <v>36339</v>
@@ -2860,18 +2850,18 @@
         <v>26.06</v>
       </c>
       <c r="K48" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L48" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B49" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C49">
         <v>14186</v>
@@ -2880,16 +2870,16 @@
         <v>30.28</v>
       </c>
       <c r="E49" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F49" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G49">
         <v>0.99239999999999995</v>
       </c>
       <c r="H49" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I49" s="1">
         <v>39593</v>
@@ -2898,18 +2888,18 @@
         <v>27.29</v>
       </c>
       <c r="K49" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L49" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B50" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C50">
         <v>900</v>
@@ -2918,16 +2908,16 @@
         <v>31.01</v>
       </c>
       <c r="E50" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F50" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G50">
         <v>0.83520000000000005</v>
       </c>
       <c r="H50" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="I50" s="1">
         <v>6637</v>
@@ -2936,18 +2926,18 @@
         <v>31.4</v>
       </c>
       <c r="K50" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L50" t="s">
-        <v>197</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C51">
         <v>900</v>
@@ -2956,16 +2946,16 @@
         <v>31.01</v>
       </c>
       <c r="E51" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F51" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G51">
         <v>0.94420000000000004</v>
       </c>
       <c r="H51" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I51" s="1">
         <v>26249</v>
@@ -2974,18 +2964,18 @@
         <v>29.17</v>
       </c>
       <c r="K51" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L51" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B52" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C52">
         <v>900</v>
@@ -2994,16 +2984,16 @@
         <v>31.01</v>
       </c>
       <c r="E52" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F52" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G52">
         <v>0.96020000000000005</v>
       </c>
       <c r="H52" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I52" s="1">
         <v>36250</v>
@@ -3012,18 +3002,18 @@
         <v>28.61</v>
       </c>
       <c r="K52" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L52" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B53" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C53">
         <v>900</v>
@@ -3032,16 +3022,16 @@
         <v>31.01</v>
       </c>
       <c r="E53" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F53" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G53">
         <v>0.98060000000000003</v>
       </c>
       <c r="H53" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I53" s="1">
         <v>35371</v>
@@ -3050,18 +3040,18 @@
         <v>26.08</v>
       </c>
       <c r="K53" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L53" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B54" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C54">
         <v>829</v>
@@ -3070,16 +3060,16 @@
         <v>31.29</v>
       </c>
       <c r="E54" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F54" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G54">
         <v>0.95620000000000005</v>
       </c>
       <c r="H54" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I54" s="1">
         <v>29291</v>
@@ -3088,18 +3078,18 @@
         <v>28.54</v>
       </c>
       <c r="K54" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L54" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>829</v>
@@ -3108,16 +3098,16 @@
         <v>31.29</v>
       </c>
       <c r="E55" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F55" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G55">
         <v>0.80879999999999996</v>
       </c>
       <c r="H55" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I55" s="1">
         <v>2412</v>
@@ -3126,18 +3116,18 @@
         <v>25.95</v>
       </c>
       <c r="K55" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L55" t="s">
-        <v>197</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B56" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C56">
         <v>829</v>
@@ -3146,16 +3136,16 @@
         <v>31.29</v>
       </c>
       <c r="E56" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F56" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G56">
         <v>0.99139999999999995</v>
       </c>
       <c r="H56" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I56" s="1">
         <v>36347</v>
@@ -3164,18 +3154,18 @@
         <v>26.05</v>
       </c>
       <c r="K56" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L56" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B57" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C57">
         <v>53</v>
@@ -3184,16 +3174,16 @@
         <v>30.4</v>
       </c>
       <c r="E57" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F57" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G57">
         <v>0.98019999999999996</v>
       </c>
       <c r="H57" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I57" s="1">
         <v>28043</v>
@@ -3202,18 +3192,18 @@
         <v>28.07</v>
       </c>
       <c r="K57" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L57" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B58" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C58">
         <v>53</v>
@@ -3222,16 +3212,16 @@
         <v>30.4</v>
       </c>
       <c r="E58" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F58" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G58">
         <v>0.95599999999999996</v>
       </c>
       <c r="H58" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I58" s="1">
         <v>42113</v>
@@ -3240,18 +3230,18 @@
         <v>26.1</v>
       </c>
       <c r="K58" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L58" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B59" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C59">
         <v>5647</v>
@@ -3260,16 +3250,16 @@
         <v>30.48</v>
       </c>
       <c r="E59" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F59" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G59">
         <v>0.75480000000000003</v>
       </c>
       <c r="H59" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="I59" s="1">
         <v>5376</v>
@@ -3278,18 +3268,18 @@
         <v>31.29</v>
       </c>
       <c r="K59" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L59" t="s">
-        <v>197</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B60" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C60">
         <v>48</v>
@@ -3298,16 +3288,16 @@
         <v>30.45</v>
       </c>
       <c r="E60" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F60" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G60">
         <v>0.99319999999999997</v>
       </c>
       <c r="H60" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I60" s="1">
         <v>45644</v>
@@ -3316,18 +3306,18 @@
         <v>27.31</v>
       </c>
       <c r="K60" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L60" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B61" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C61">
         <v>8926</v>
@@ -3336,16 +3326,16 @@
         <v>31.28</v>
       </c>
       <c r="E61" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F61" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G61">
         <v>0.98399999999999999</v>
       </c>
       <c r="H61" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I61" s="1">
         <v>33987</v>
@@ -3354,18 +3344,18 @@
         <v>26.24</v>
       </c>
       <c r="K61" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L61" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B62" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C62">
         <v>2392</v>
@@ -3374,16 +3364,16 @@
         <v>30.41</v>
       </c>
       <c r="E62" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F62" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G62">
         <v>0.97</v>
       </c>
       <c r="H62" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I62" s="1">
         <v>27532</v>
@@ -3392,18 +3382,18 @@
         <v>27.92</v>
       </c>
       <c r="K62" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L62" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B63" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C63">
         <v>51</v>
@@ -3412,16 +3402,16 @@
         <v>30.33</v>
       </c>
       <c r="E63" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F63" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G63">
         <v>0.98740000000000006</v>
       </c>
       <c r="H63" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I63" s="1">
         <v>36038</v>
@@ -3430,18 +3420,18 @@
         <v>26.03</v>
       </c>
       <c r="K63" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L63" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B64" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C64">
         <v>42</v>
@@ -3450,16 +3440,16 @@
         <v>30.51</v>
       </c>
       <c r="E64" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G64">
         <v>0.97160000000000002</v>
       </c>
       <c r="H64" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I64" s="1">
         <v>28955</v>
@@ -3468,18 +3458,18 @@
         <v>28.15</v>
       </c>
       <c r="K64" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L64" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B65" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C65">
         <v>61</v>
@@ -3488,16 +3478,16 @@
         <v>30.52</v>
       </c>
       <c r="E65" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F65" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G65">
         <v>0.97060000000000002</v>
       </c>
       <c r="H65" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I65" s="1">
         <v>27545</v>
@@ -3506,18 +3496,18 @@
         <v>27.93</v>
       </c>
       <c r="K65" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L65" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B66" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C66">
         <v>61</v>
@@ -3526,16 +3516,16 @@
         <v>30.36</v>
       </c>
       <c r="E66" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F66" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G66">
         <v>0.9798</v>
       </c>
       <c r="H66" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I66" s="1">
         <v>28046</v>
@@ -3544,18 +3534,18 @@
         <v>28.08</v>
       </c>
       <c r="K66" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L66" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B67" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C67">
         <v>61</v>
@@ -3564,16 +3554,16 @@
         <v>30.36</v>
       </c>
       <c r="E67" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F67" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G67">
         <v>0.99299999999999999</v>
       </c>
       <c r="H67" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I67" s="1">
         <v>36926</v>
@@ -3582,18 +3572,18 @@
         <v>26</v>
       </c>
       <c r="K67" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L67" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B68" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C68">
         <v>50</v>
@@ -3602,16 +3592,16 @@
         <v>30.35</v>
       </c>
       <c r="E68" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F68" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G68">
         <v>0.98019999999999996</v>
       </c>
       <c r="H68" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I68" s="1">
         <v>28047</v>
@@ -3620,18 +3610,18 @@
         <v>28.07</v>
       </c>
       <c r="K68" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L68" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B69" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C69">
         <v>50</v>
@@ -3640,16 +3630,16 @@
         <v>30.35</v>
       </c>
       <c r="E69" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F69" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G69">
         <v>0.99219999999999997</v>
       </c>
       <c r="H69" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I69" s="1">
         <v>36560</v>
@@ -3658,18 +3648,18 @@
         <v>25.98</v>
       </c>
       <c r="K69" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L69" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B70" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C70">
         <v>2357</v>
@@ -3678,16 +3668,16 @@
         <v>30.18</v>
       </c>
       <c r="E70" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F70" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G70">
         <v>0.98040000000000005</v>
       </c>
       <c r="H70" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I70" s="1">
         <v>28032</v>
@@ -3696,18 +3686,18 @@
         <v>28.08</v>
       </c>
       <c r="K70" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L70" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B71" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C71">
         <v>2357</v>
@@ -3716,16 +3706,16 @@
         <v>30.18</v>
       </c>
       <c r="E71" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F71" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G71">
         <v>0.99119999999999997</v>
       </c>
       <c r="H71" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I71" s="1">
         <v>36322</v>
@@ -3734,18 +3724,18 @@
         <v>26.06</v>
       </c>
       <c r="K71" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L71" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B72" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C72">
         <v>2357</v>
@@ -3754,16 +3744,16 @@
         <v>30.18</v>
       </c>
       <c r="E72" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F72" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G72">
         <v>0.9738</v>
       </c>
       <c r="H72" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I72" s="1">
         <v>38016</v>
@@ -3772,18 +3762,18 @@
         <v>27.58</v>
       </c>
       <c r="K72" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L72" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B73" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C73">
         <v>1096</v>
@@ -3792,16 +3782,16 @@
         <v>31.3</v>
       </c>
       <c r="E73" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F73" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G73">
         <v>0.76519999999999999</v>
       </c>
       <c r="H73" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I73" s="1">
         <v>2718</v>
@@ -3810,18 +3800,18 @@
         <v>29.43</v>
       </c>
       <c r="K73" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L73" t="s">
-        <v>197</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B74" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C74">
         <v>45</v>
@@ -3830,16 +3820,16 @@
         <v>30.53</v>
       </c>
       <c r="E74" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F74" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G74">
         <v>0.98360000000000003</v>
       </c>
       <c r="H74" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I74" s="1">
         <v>40177</v>
@@ -3848,18 +3838,18 @@
         <v>29.52</v>
       </c>
       <c r="K74" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L74" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B75" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C75">
         <v>2256</v>
@@ -3868,16 +3858,16 @@
         <v>31.24</v>
       </c>
       <c r="E75" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F75" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G75">
         <v>0.92979999999999996</v>
       </c>
       <c r="H75" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I75" s="1">
         <v>41836</v>
@@ -3886,18 +3876,18 @@
         <v>28.05</v>
       </c>
       <c r="K75" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L75" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B76" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C76">
         <v>2256</v>
@@ -3906,16 +3896,16 @@
         <v>31.24</v>
       </c>
       <c r="E76" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F76" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G76">
         <v>0.98640000000000005</v>
       </c>
       <c r="H76" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I76" s="1">
         <v>34734</v>
@@ -3924,18 +3914,18 @@
         <v>26.09</v>
       </c>
       <c r="K76" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L76" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B77" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C77">
         <v>2256</v>
@@ -3944,16 +3934,16 @@
         <v>31.23</v>
       </c>
       <c r="E77" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F77" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G77">
         <v>0.9496</v>
       </c>
       <c r="H77" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I77" s="1">
         <v>39139</v>
@@ -3962,18 +3952,18 @@
         <v>27.92</v>
       </c>
       <c r="K77" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L77" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B78" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C78">
         <v>2256</v>
@@ -3982,16 +3972,16 @@
         <v>31.23</v>
       </c>
       <c r="E78" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F78" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G78">
         <v>0.98660000000000003</v>
       </c>
       <c r="H78" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I78" s="1">
         <v>34724</v>
@@ -4000,18 +3990,18 @@
         <v>26.1</v>
       </c>
       <c r="K78" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L78" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B79" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C79">
         <v>3230</v>
@@ -4020,16 +4010,16 @@
         <v>31.18</v>
       </c>
       <c r="E79" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="G79">
         <v>0.75819999999999999</v>
       </c>
       <c r="H79" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I79" s="1">
         <v>39230</v>
@@ -4038,18 +4028,18 @@
         <v>33.090000000000003</v>
       </c>
       <c r="K79" t="s">
+        <v>21</v>
+      </c>
+      <c r="L79" t="s">
         <v>18</v>
-      </c>
-      <c r="L79" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B80" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C80">
         <v>3230</v>
@@ -4058,16 +4048,16 @@
         <v>31.18</v>
       </c>
       <c r="E80" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F80" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G80">
         <v>0.98440000000000005</v>
       </c>
       <c r="H80" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I80" s="1">
         <v>35240</v>
@@ -4076,18 +4066,18 @@
         <v>26.32</v>
       </c>
       <c r="K80" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L80" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B81" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C81">
         <v>3230</v>
@@ -4096,16 +4086,16 @@
         <v>31.18</v>
       </c>
       <c r="E81" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F81" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G81">
         <v>0.96460000000000001</v>
       </c>
       <c r="H81" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I81" s="1">
         <v>25645</v>
@@ -4114,10 +4104,10 @@
         <v>29.04</v>
       </c>
       <c r="K81" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L81" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -4127,1042 +4117,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5E122E1-A68F-4063-BA64-396106B648B8}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2">
-        <v>520</v>
-      </c>
-      <c r="D2">
-        <v>30.34</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2">
-        <v>0.99239999999999995</v>
-      </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="1">
-        <v>39597</v>
-      </c>
-      <c r="J2">
-        <v>27.28</v>
-      </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3">
-        <v>677</v>
-      </c>
-      <c r="D3">
-        <v>30.37</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3">
-        <v>0.93820000000000003</v>
-      </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="1">
-        <v>40676</v>
-      </c>
-      <c r="J3">
-        <v>26.01</v>
-      </c>
-      <c r="K3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>48</v>
-      </c>
-      <c r="D4">
-        <v>30.45</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4">
-        <v>0.98839999999999995</v>
-      </c>
-      <c r="H4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="1">
-        <v>43663</v>
-      </c>
-      <c r="J4">
-        <v>27.42</v>
-      </c>
-      <c r="K4" t="s">
-        <v>18</v>
-      </c>
-      <c r="L4" t="s">
-        <v>43</v>
-      </c>
-      <c r="M4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>1030</v>
-      </c>
-      <c r="D5">
-        <v>30.17</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5">
-        <v>0.96660000000000001</v>
-      </c>
-      <c r="H5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="1">
-        <v>38820</v>
-      </c>
-      <c r="J5">
-        <v>27.36</v>
-      </c>
-      <c r="K5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L5" t="s">
-        <v>43</v>
-      </c>
-      <c r="M5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6">
-        <v>42</v>
-      </c>
-      <c r="D6">
-        <v>30.48</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="1">
-        <v>43614</v>
-      </c>
-      <c r="J6">
-        <v>27.4</v>
-      </c>
-      <c r="K6" t="s">
-        <v>15</v>
-      </c>
-      <c r="L6" t="s">
-        <v>43</v>
-      </c>
-      <c r="M6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>3610</v>
-      </c>
-      <c r="D7">
-        <v>30.27</v>
-      </c>
-      <c r="E7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7">
-        <v>0.99380000000000002</v>
-      </c>
-      <c r="H7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="1">
-        <v>42058</v>
-      </c>
-      <c r="J7">
-        <v>27.08</v>
-      </c>
-      <c r="K7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L7" t="s">
-        <v>43</v>
-      </c>
-      <c r="M7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8">
-        <v>520</v>
-      </c>
-      <c r="D8">
-        <v>30.46</v>
-      </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8">
-        <v>0.99380000000000002</v>
-      </c>
-      <c r="H8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="1">
-        <v>42062</v>
-      </c>
-      <c r="J8">
-        <v>27.08</v>
-      </c>
-      <c r="K8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L8" t="s">
-        <v>43</v>
-      </c>
-      <c r="M8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9">
-        <v>22</v>
-      </c>
-      <c r="D9">
-        <v>30.43</v>
-      </c>
-      <c r="E9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G9">
-        <v>0.98660000000000003</v>
-      </c>
-      <c r="H9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="1">
-        <v>39851</v>
-      </c>
-      <c r="J9">
-        <v>27.34</v>
-      </c>
-      <c r="K9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10">
-        <v>4009</v>
-      </c>
-      <c r="D10">
-        <v>31.35</v>
-      </c>
-      <c r="E10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10">
-        <v>0.94079999999999997</v>
-      </c>
-      <c r="H10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="1">
-        <v>36479</v>
-      </c>
-      <c r="J10">
-        <v>28.16</v>
-      </c>
-      <c r="K10" t="s">
-        <v>18</v>
-      </c>
-      <c r="L10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11">
-        <v>48</v>
-      </c>
-      <c r="D11">
-        <v>30.45</v>
-      </c>
-      <c r="E11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" t="s">
-        <v>66</v>
-      </c>
-      <c r="G11">
-        <v>0.98819999999999997</v>
-      </c>
-      <c r="H11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="1">
-        <v>43665</v>
-      </c>
-      <c r="J11">
-        <v>27.4</v>
-      </c>
-      <c r="K11" t="s">
-        <v>18</v>
-      </c>
-      <c r="L11" t="s">
-        <v>43</v>
-      </c>
-      <c r="M11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>69</v>
-      </c>
-      <c r="B12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12">
-        <v>48</v>
-      </c>
-      <c r="D12">
-        <v>30.47</v>
-      </c>
-      <c r="E12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" t="s">
-        <v>70</v>
-      </c>
-      <c r="G12">
-        <v>0.98880000000000001</v>
-      </c>
-      <c r="H12" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="1">
-        <v>43678</v>
-      </c>
-      <c r="J12">
-        <v>27.42</v>
-      </c>
-      <c r="K12" t="s">
-        <v>18</v>
-      </c>
-      <c r="L12" t="s">
-        <v>43</v>
-      </c>
-      <c r="M12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13">
-        <v>12762</v>
-      </c>
-      <c r="D13">
-        <v>30.37</v>
-      </c>
-      <c r="E13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13">
-        <v>0.99260000000000004</v>
-      </c>
-      <c r="H13" t="s">
-        <v>17</v>
-      </c>
-      <c r="I13" s="1">
-        <v>39586</v>
-      </c>
-      <c r="J13">
-        <v>27.28</v>
-      </c>
-      <c r="K13" t="s">
-        <v>18</v>
-      </c>
-      <c r="L13" t="s">
-        <v>43</v>
-      </c>
-      <c r="M13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14">
-        <v>422</v>
-      </c>
-      <c r="D14">
-        <v>30.32</v>
-      </c>
-      <c r="E14" t="s">
-        <v>38</v>
-      </c>
-      <c r="F14" t="s">
-        <v>80</v>
-      </c>
-      <c r="G14">
-        <v>0.99519999999999997</v>
-      </c>
-      <c r="H14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I14" s="1">
-        <v>40695</v>
-      </c>
-      <c r="J14">
-        <v>27.4</v>
-      </c>
-      <c r="K14" t="s">
-        <v>18</v>
-      </c>
-      <c r="L14" t="s">
-        <v>43</v>
-      </c>
-      <c r="M14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15">
-        <v>6964</v>
-      </c>
-      <c r="D15">
-        <v>30.47</v>
-      </c>
-      <c r="E15" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" t="s">
-        <v>82</v>
-      </c>
-      <c r="G15">
-        <v>0.99299999999999999</v>
-      </c>
-      <c r="H15" t="s">
-        <v>17</v>
-      </c>
-      <c r="I15" s="1">
-        <v>45668</v>
-      </c>
-      <c r="J15">
-        <v>27.3</v>
-      </c>
-      <c r="K15" t="s">
-        <v>18</v>
-      </c>
-      <c r="L15" t="s">
-        <v>43</v>
-      </c>
-      <c r="M15" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B16" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16">
-        <v>14595</v>
-      </c>
-      <c r="D16">
-        <v>31.39</v>
-      </c>
-      <c r="E16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" t="s">
-        <v>96</v>
-      </c>
-      <c r="G16">
-        <v>0.98819999999999997</v>
-      </c>
-      <c r="H16" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="1">
-        <v>43676</v>
-      </c>
-      <c r="J16">
-        <v>27.42</v>
-      </c>
-      <c r="K16" t="s">
-        <v>18</v>
-      </c>
-      <c r="L16" t="s">
-        <v>43</v>
-      </c>
-      <c r="M16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>97</v>
-      </c>
-      <c r="B17" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17">
-        <v>900</v>
-      </c>
-      <c r="D17">
-        <v>30.89</v>
-      </c>
-      <c r="E17" t="s">
-        <v>38</v>
-      </c>
-      <c r="F17" t="s">
-        <v>105</v>
-      </c>
-      <c r="G17">
-        <v>0.95779999999999998</v>
-      </c>
-      <c r="H17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I17" s="1">
-        <v>35851</v>
-      </c>
-      <c r="J17">
-        <v>28.62</v>
-      </c>
-      <c r="K17" t="s">
-        <v>18</v>
-      </c>
-      <c r="L17" t="s">
-        <v>43</v>
-      </c>
-      <c r="M17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>108</v>
-      </c>
-      <c r="B18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18">
-        <v>5734</v>
-      </c>
-      <c r="D18">
-        <v>31.36</v>
-      </c>
-      <c r="E18" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" t="s">
-        <v>109</v>
-      </c>
-      <c r="G18">
-        <v>0.9748</v>
-      </c>
-      <c r="H18" t="s">
-        <v>17</v>
-      </c>
-      <c r="I18" s="1">
-        <v>46278</v>
-      </c>
-      <c r="J18">
-        <v>28.3</v>
-      </c>
-      <c r="K18" t="s">
-        <v>18</v>
-      </c>
-      <c r="L18" t="s">
-        <v>43</v>
-      </c>
-      <c r="M18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>110</v>
-      </c>
-      <c r="B19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19">
-        <v>14186</v>
-      </c>
-      <c r="D19">
-        <v>30.28</v>
-      </c>
-      <c r="E19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" t="s">
-        <v>112</v>
-      </c>
-      <c r="G19">
-        <v>0.99239999999999995</v>
-      </c>
-      <c r="H19" t="s">
-        <v>17</v>
-      </c>
-      <c r="I19" s="1">
-        <v>39593</v>
-      </c>
-      <c r="J19">
-        <v>27.29</v>
-      </c>
-      <c r="K19" t="s">
-        <v>18</v>
-      </c>
-      <c r="L19" t="s">
-        <v>43</v>
-      </c>
-      <c r="M19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>113</v>
-      </c>
-      <c r="B20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20">
-        <v>900</v>
-      </c>
-      <c r="D20">
-        <v>31.01</v>
-      </c>
-      <c r="E20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" t="s">
-        <v>117</v>
-      </c>
-      <c r="G20">
-        <v>0.96020000000000005</v>
-      </c>
-      <c r="H20" t="s">
-        <v>17</v>
-      </c>
-      <c r="I20" s="1">
-        <v>36250</v>
-      </c>
-      <c r="J20">
-        <v>28.61</v>
-      </c>
-      <c r="K20" t="s">
-        <v>18</v>
-      </c>
-      <c r="L20" t="s">
-        <v>43</v>
-      </c>
-      <c r="M20" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>123</v>
-      </c>
-      <c r="B21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21">
-        <v>53</v>
-      </c>
-      <c r="D21">
-        <v>30.4</v>
-      </c>
-      <c r="E21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" t="s">
-        <v>125</v>
-      </c>
-      <c r="G21">
-        <v>0.95599999999999996</v>
-      </c>
-      <c r="H21" t="s">
-        <v>17</v>
-      </c>
-      <c r="I21" s="1">
-        <v>42113</v>
-      </c>
-      <c r="J21">
-        <v>26.1</v>
-      </c>
-      <c r="K21" t="s">
-        <v>18</v>
-      </c>
-      <c r="L21" t="s">
-        <v>43</v>
-      </c>
-      <c r="M21" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>129</v>
-      </c>
-      <c r="B22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22">
-        <v>48</v>
-      </c>
-      <c r="D22">
-        <v>30.45</v>
-      </c>
-      <c r="E22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" t="s">
-        <v>130</v>
-      </c>
-      <c r="G22">
-        <v>0.99319999999999997</v>
-      </c>
-      <c r="H22" t="s">
-        <v>17</v>
-      </c>
-      <c r="I22" s="1">
-        <v>45644</v>
-      </c>
-      <c r="J22">
-        <v>27.31</v>
-      </c>
-      <c r="K22" t="s">
-        <v>18</v>
-      </c>
-      <c r="L22" t="s">
-        <v>43</v>
-      </c>
-      <c r="M22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>147</v>
-      </c>
-      <c r="B23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23">
-        <v>2357</v>
-      </c>
-      <c r="D23">
-        <v>30.18</v>
-      </c>
-      <c r="E23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" t="s">
-        <v>150</v>
-      </c>
-      <c r="G23">
-        <v>0.9738</v>
-      </c>
-      <c r="H23" t="s">
-        <v>17</v>
-      </c>
-      <c r="I23" s="1">
-        <v>38016</v>
-      </c>
-      <c r="J23">
-        <v>27.58</v>
-      </c>
-      <c r="K23" t="s">
-        <v>18</v>
-      </c>
-      <c r="L23" t="s">
-        <v>43</v>
-      </c>
-      <c r="M23" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>153</v>
-      </c>
-      <c r="B24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24">
-        <v>45</v>
-      </c>
-      <c r="D24">
-        <v>30.53</v>
-      </c>
-      <c r="E24" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" t="s">
-        <v>154</v>
-      </c>
-      <c r="G24">
-        <v>0.98360000000000003</v>
-      </c>
-      <c r="H24" t="s">
-        <v>17</v>
-      </c>
-      <c r="I24" s="1">
-        <v>40177</v>
-      </c>
-      <c r="J24">
-        <v>29.52</v>
-      </c>
-      <c r="K24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L24" t="s">
-        <v>43</v>
-      </c>
-      <c r="M24" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>155</v>
-      </c>
-      <c r="B25" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25">
-        <v>2256</v>
-      </c>
-      <c r="D25">
-        <v>31.24</v>
-      </c>
-      <c r="E25" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" t="s">
-        <v>156</v>
-      </c>
-      <c r="G25">
-        <v>0.92979999999999996</v>
-      </c>
-      <c r="H25" t="s">
-        <v>17</v>
-      </c>
-      <c r="I25" s="1">
-        <v>41836</v>
-      </c>
-      <c r="J25">
-        <v>28.05</v>
-      </c>
-      <c r="K25" t="s">
-        <v>18</v>
-      </c>
-      <c r="L25" t="s">
-        <v>43</v>
-      </c>
-      <c r="M25" t="s">
-        <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD8B3F6F-3EA6-4A1A-89EC-A93356C24FCF}">
   <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5178,16 +4132,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>1</v>
@@ -5196,30 +4150,30 @@
         <v>2</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G2">
         <v>3072</v>
@@ -5228,27 +4182,27 @@
         <v>828</v>
       </c>
       <c r="I2" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>508</v>
@@ -5257,27 +4211,27 @@
         <v>508</v>
       </c>
       <c r="I3" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>174</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>12749</v>
@@ -5286,27 +4240,27 @@
         <v>353</v>
       </c>
       <c r="I4" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>173</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>227</v>
@@ -5315,27 +4269,27 @@
         <v>206</v>
       </c>
       <c r="I5" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>354</v>
@@ -5344,27 +4298,27 @@
         <v>354</v>
       </c>
       <c r="I6" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>257</v>
@@ -5373,27 +4327,27 @@
         <v>257</v>
       </c>
       <c r="I7" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>474</v>
@@ -5402,56 +4356,56 @@
         <v>48</v>
       </c>
       <c r="I8" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>3538</v>
       </c>
-      <c r="H9" t="s">
-        <v>47</v>
+      <c r="H9" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="I9" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>403</v>
@@ -5460,27 +4414,27 @@
         <v>403</v>
       </c>
       <c r="I10" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>190</v>
@@ -5489,27 +4443,27 @@
         <v>21</v>
       </c>
       <c r="I11" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G12">
         <v>45</v>
@@ -5518,27 +4472,27 @@
         <v>45</v>
       </c>
       <c r="I12" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>677</v>
@@ -5547,27 +4501,27 @@
         <v>677</v>
       </c>
       <c r="I13" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G14">
         <v>583</v>
@@ -5576,27 +4530,27 @@
         <v>45</v>
       </c>
       <c r="I14" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G15">
         <v>61</v>
@@ -5605,7 +4559,7 @@
         <v>61</v>
       </c>
       <c r="I15" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -5614,13 +4568,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c478fcf1-df2b-4b17-ac0d-5fb1dd3b8dd4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5835,39 +4788,48 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c478fcf1-df2b-4b17-ac0d-5fb1dd3b8dd4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31E87D9F-66D2-4C2C-A67E-96CB5D0CC685}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AE006EE-9A89-44A1-89F7-BBD6E45BF84E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="2a1e774b-1312-493c-b167-5aa786dea5b7"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="c478fcf1-df2b-4b17-ac0d-5fb1dd3b8dd4"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{179E1503-B062-4719-AFED-334C55D82976}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{179E1503-B062-4719-AFED-334C55D82976}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c478fcf1-df2b-4b17-ac0d-5fb1dd3b8dd4"/>
+    <ds:schemaRef ds:uri="2a1e774b-1312-493c-b167-5aa786dea5b7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AE006EE-9A89-44A1-89F7-BBD6E45BF84E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31E87D9F-66D2-4C2C-A67E-96CB5D0CC685}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c478fcf1-df2b-4b17-ac0d-5fb1dd3b8dd4"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>